--- a/15. Advance Analytics/Advance_Analytics.xlsx
+++ b/15. Advance Analytics/Advance_Analytics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Advance_Excel_BI\15. Advance Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0595D8C2-5E3E-4B8F-B830-25E0EB0471F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C372486E-C434-42AA-A2F5-3AF5CD819DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario Summary" sheetId="15" r:id="rId1"/>
@@ -123,9 +123,6 @@
     <t>Net Profit</t>
   </si>
   <si>
-    <t>Quatity</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
@@ -280,6 +277,9 @@
   </si>
   <si>
     <t>$H$14</t>
+  </si>
+  <si>
+    <t>Quantity</t>
   </si>
 </sst>
 </file>
@@ -877,6 +877,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -915,18 +927,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1273,38 +1273,38 @@
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="30.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
       <c r="E4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -1322,7 +1322,7 @@
     <row r="6" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B6" s="31"/>
       <c r="C6" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="1">
         <v>0.9</v>
@@ -1419,38 +1419,38 @@
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="30.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
       <c r="E4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -1468,7 +1468,7 @@
     <row r="6" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B6" s="31"/>
       <c r="C6" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="1">
         <v>0.75</v>
@@ -1504,7 +1504,7 @@
     <row r="8" spans="2:9" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="33"/>
       <c r="C8" s="33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" s="2">
         <v>4500</v>
@@ -1559,29 +1559,29 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:10" ht="37.200000000000003" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B2" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53"/>
+      <c r="B2" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="3" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
+      <c r="C4" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="43"/>
+      <c r="E4" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="18">
         <v>100</v>
       </c>
@@ -1595,10 +1595,10 @@
       <c r="G5" s="36"/>
     </row>
     <row r="6" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="41"/>
+      <c r="C6" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="45"/>
       <c r="E6" s="36" t="s">
         <v>0</v>
       </c>
@@ -1609,10 +1609,10 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7" s="36"/>
       <c r="G7" s="36"/>
@@ -1628,15 +1628,15 @@
       <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:10" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="50" t="s">
+      <c r="C9" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
       <c r="H9" s="19">
         <v>0.75</v>
       </c>
@@ -1649,12 +1649,12 @@
       <c r="G10" s="36"/>
     </row>
     <row r="11" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="47"/>
+      <c r="C11" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="51"/>
       <c r="E11" s="36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="36"/>
       <c r="G11" s="36"/>
@@ -1664,10 +1664,10 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="36"/>
       <c r="G12" s="36"/>
@@ -1684,10 +1684,10 @@
       <c r="G13" s="36"/>
     </row>
     <row r="14" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="45"/>
+      <c r="C14" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="49"/>
       <c r="E14" s="36" t="s">
         <v>1</v>
       </c>
@@ -1732,7 +1732,6 @@
     </scenario>
   </scenarios>
   <mergeCells count="20">
-    <mergeCell ref="E11:G11"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="E6:G6"/>
@@ -1752,6 +1751,7 @@
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1764,7 +1764,9 @@
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="10" width="12.6640625" customWidth="1"/>
+    <col min="2" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="9" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="3.6640625" customWidth="1"/>
     <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
     <col min="13" max="16384" width="12.6640625" hidden="1"/>
@@ -1772,17 +1774,17 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:10" ht="37.200000000000003" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B2" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53"/>
+      <c r="B2" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="3" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1795,12 +1797,12 @@
         <v>12</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="8" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="D6" s="20">
         <v>8.3333333333333339</v>
@@ -1812,7 +1814,7 @@
         <v>13.333333333333332</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" s="8">
         <v>1000</v>
@@ -1820,7 +1822,7 @@
     </row>
     <row r="7" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" s="8">
         <v>60</v>
@@ -1835,7 +1837,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1852,7 +1854,7 @@
         <v>40</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I9" s="8">
         <f>D6*D11+E6*E11+F6*F11</f>
@@ -1861,7 +1863,7 @@
     </row>
     <row r="10" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H10" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10" s="8">
         <f>D6*D12+E6*E12+F6*F12</f>
@@ -1870,7 +1872,7 @@
     </row>
     <row r="11" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="8">
         <v>40</v>
@@ -1885,7 +1887,7 @@
     </row>
     <row r="12" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C12" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="8">
         <v>4</v>
@@ -1946,19 +1948,19 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="12"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>0.92601088576095858</v>
@@ -1966,7 +1968,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>0.85749616054779509</v>
@@ -1974,7 +1976,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>0.80049462476691313</v>
@@ -1982,7 +1984,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>210.54759632817266</v>
@@ -1990,7 +1992,7 @@
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2">
         <v>8</v>
@@ -1998,30 +2000,30 @@
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -2041,7 +2043,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -2055,7 +2057,7 @@
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2">
         <v>7</v>
@@ -2071,33 +2073,33 @@
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
       <c r="B16" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="H16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="I16" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>268.88125016900551</v>
@@ -2126,7 +2128,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>1.2004014948250672</v>
@@ -2155,7 +2157,7 @@
     </row>
     <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="2">
         <v>1.7056722131842386</v>
@@ -2206,15 +2208,15 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:8" ht="37.200000000000003" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B2" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="53"/>
+      <c r="B2" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="2:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D3">
@@ -2229,13 +2231,13 @@
     </row>
     <row r="4" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D4" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>24</v>
-      </c>
       <c r="F4" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
